--- a/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
+++ b/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
@@ -6013,11 +6013,6 @@
           <t>1:51.633</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8390,11 +8385,6 @@
           <t>3:08.236</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14339,11 +14329,6 @@
           <t>1:52.705</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18670,11 +18655,6 @@
           <t>3:09.942</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -23851,11 +23831,6 @@
           <t>3:11.352</t>
         </is>
       </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -44248,11 +44223,6 @@
           <t>0:36.961</t>
         </is>
       </c>
-      <c r="R688" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -45368,11 +45338,6 @@
           <t>0:42.738</t>
         </is>
       </c>
-      <c r="R706" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -55255,11 +55220,6 @@
           <t>0:36.816</t>
         </is>
       </c>
-      <c r="R864" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -58250,11 +58210,6 @@
           <t>0:43.037</t>
         </is>
       </c>
-      <c r="R912" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -66413,11 +66368,6 @@
           <t>0:36.809</t>
         </is>
       </c>
-      <c r="R1040" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -67698,11 +67648,6 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>0:43.084</t>
-        </is>
-      </c>
-      <c r="R1060" t="inlineStr">
-        <is>
-          <t>51823</t>
         </is>
       </c>
     </row>
@@ -80145,7 +80090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80437,105 +80382,105 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scotty</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BICKNELL</t>
+          <t>BLAHOVA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BLAHOVA</t>
+          <t>BORZOV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Yuliya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BORZOV</t>
+          <t>BORZOVA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yuliya</t>
+          <t>Jose Luis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BORZOVA</t>
+          <t>BOUZA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jose Luis</t>
+          <t>Khadim</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOUZA</t>
+          <t>BOYE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -80547,17 +80492,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Khadim</t>
+          <t>Bram</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOYE</t>
+          <t>BRANDJES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -80569,17 +80514,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bram</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BRANDJES</t>
+          <t>BRENDEL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -80591,171 +80536,171 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BRENDEL</t>
+          <t>BRUN-LIE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRUN-LIE</t>
+          <t>BURGER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BURGER</t>
+          <t>CAMPANA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Cyrille</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAMPANA</t>
+          <t>CARRE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cyrille</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CARRE</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CASTANEDA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CASTANEDA</t>
+          <t>CICALI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -80767,39 +80712,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stefania</t>
+          <t>Chrisjan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CICALI</t>
+          <t>COETZEE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Saul</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>CRAVIOTTO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -80811,17 +80756,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chrisjan</t>
+          <t>Everardo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>COETZEE</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -80833,39 +80778,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Saul</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CRAVIOTTO</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Everardo</t>
+          <t>Miklos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>DUDAS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -80877,61 +80822,61 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>DYACHENKO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Miklos</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUDAS</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>42928</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DYACHENKO</t>
+          <t>FARINEAUX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -80943,39 +80888,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FARINEAUX</t>
+          <t>FITZGERALD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -80987,17 +80932,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FLORCZAK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -81009,17 +80954,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>42128</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Osbaldo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FITZGERALD</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -81031,39 +80976,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Anastasia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FLORCZAK</t>
+          <t>GLININA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Osbaldo</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -81075,61 +81020,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>46829</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GLININA</t>
+          <t>GERMADE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Vyacheslav</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GERMADE</t>
+          <t>GORN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -81141,39 +81086,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GORN</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -81185,17 +81130,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -81207,17 +81152,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Mustafa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>GULBAHAR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -81229,39 +81174,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>GUYOT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mustafa</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GULBAHAR</t>
+          <t>HAGARA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -81273,39 +81218,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GUYOT</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Gordan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HAGARA</t>
+          <t>HARBRECHT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -81317,105 +81262,105 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gordan</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HARBRECHT</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HERNANZ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HERNANZ</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -81427,17 +81372,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -81449,17 +81394,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -81471,17 +81416,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -81493,39 +81438,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>HUBERT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -81537,39 +81482,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>HUFNAGEL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HUBERT</t>
+          <t>HYBOIS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -81581,17 +81526,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Vilyam</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HUFNAGEL</t>
+          <t>IBRAGIMOV</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -81603,17 +81548,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HYBOIS</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -81625,17 +81570,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vilyam</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IBRAGIMOV</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -81647,127 +81592,127 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Shiho</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KAKIZAKI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KAZAKOVA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shiho</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KAKIZAKI</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KAZAKOVA</t>
+          <t>KIRCHEV</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KIRCHEV</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -81779,39 +81724,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>LECRUBIER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -81823,39 +81768,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LECRUBIER</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -81867,61 +81812,61 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Aliksandr</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LIAPIOSHKA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Haiping</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aliksandr</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LIAPIOSHKA</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -81933,39 +81878,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Haiping</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LYAPUNOV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Vadzim</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>MAKHNEU</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -81977,17 +81922,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jaimee</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LOVETT</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -81999,17 +81944,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Momotaro</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LYAPUNOV</t>
+          <t>MATSUSHITA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -82021,17 +81966,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vadzim</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MAKHNEU</t>
+          <t>MEDVEDEV</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -82043,39 +81988,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Momotaro</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MATSUSHITA</t>
+          <t>MIADZVEDZEU</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -82087,17 +82032,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEDVEDEV</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -82109,17 +82054,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MISKOVSKY</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -82131,17 +82076,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MIADZVEDZEU</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -82153,17 +82098,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Keiji</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MIZUMOTO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -82175,17 +82120,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MISKOVSKY</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -82197,17 +82142,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>MOLOCHKOV</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -82219,39 +82164,39 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Keiji</t>
+          <t>Maricela</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MIZUMOTO</t>
+          <t>MONTEMAYOR RODRIGUEZ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Aleksey</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MOCHALOV</t>
+          <t>MOUGET</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -82263,17 +82208,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Mohamed Ali</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MOLOCHKOV</t>
+          <t>MRABET</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -82285,17 +82230,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Maricela</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MONTEMAYOR RODRIGUEZ</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -82307,17 +82252,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MOUGET</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -82329,39 +82274,39 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mohamed Ali</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MRABET</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Asumi</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>OHMURA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -82373,61 +82318,61 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>84923</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Yuka</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>ONO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Asumi</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OHMURA</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -82439,83 +82384,83 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>84923</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Yuka</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ONO</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PETRACCA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PIATRUSHENKA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -82527,17 +82472,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PETRACCA</t>
+          <t>PONOMARENKO JANIC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -82549,39 +82494,39 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>65581</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PIATRUSHENKA</t>
+          <t>PORTELA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>RABCHANKA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -82593,61 +82538,61 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PONOMARENKO JANIC</t>
+          <t>RAMELLA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PORTELA</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RABCHANKA</t>
+          <t>REBSTOCK</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -82659,17 +82604,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RAMELLA</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -82681,17 +82626,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>RICHARD</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -82703,17 +82648,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Nicola</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>REBSTOCK</t>
+          <t>RIPAMONTI</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -82725,39 +82670,39 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>RICHARD</t>
+          <t>RUMJANCEVS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -82769,17 +82714,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nicola</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RIPAMONTI</t>
+          <t>RYAKHOV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -82791,17 +82736,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Iuliana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>SALAKHOVA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -82813,17 +82758,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RUMJANCEVS</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -82835,39 +82780,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RYAKHOV</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Iuliana</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SALAKHOVA</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -82879,39 +82824,39 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>140348</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Madjiguene</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SECK</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -82923,17 +82868,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -82945,83 +82890,83 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>140348</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Madjiguene</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SECK</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SIMART</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -83033,17 +82978,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Emil Staer</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SIMART</t>
+          <t>SIMENSEN</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -83055,17 +83000,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -83077,17 +83022,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -83099,17 +83044,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Emil Staer</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SIMENSEN</t>
+          <t>TOMICEVIC</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -83121,17 +83066,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>43664</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Serguey</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>TORRES MADRIGAL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -83143,39 +83088,39 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>TROEL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TOMICEVIC</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -83187,17 +83132,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Serguey</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TORRES MADRIGAL</t>
+          <t>VAITSISHKIN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -83209,39 +83154,39 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jesus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TROEL</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Taras</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VALKO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -83253,17 +83198,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VAITSISHKIN</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -83275,17 +83220,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jesus</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -83297,17 +83242,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Taras</t>
+          <t>Henrik</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>VALKO</t>
+          <t>VASBANYAI</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -83319,39 +83264,39 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASILYEV</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -83363,17 +83308,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Henrik</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VASBANYAI</t>
+          <t>VAUCHETSKI</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -83385,83 +83330,83 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>VERCH</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VASILYEV</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>VAUCHETSKI</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VERCH</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -83473,17 +83418,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -83495,39 +83440,39 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -83539,39 +83484,39 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Haitao</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Cagribey</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WYLENZEK</t>
+          <t>YILDIRIM</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -83583,17 +83528,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Oleg</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>ZHESTKOV</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -83605,86 +83550,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Haitao</t>
+          <t>Nejc</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XU</t>
+          <t>ZNIDARCIC</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Cagribey</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>YILDIRIM</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>36152</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Oleg</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>ZHESTKOV</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>37764</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Nejc</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>ZNIDARCIC</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
+++ b/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
@@ -1536,6 +1536,11 @@
           <t>3:24.480</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2161,6 +2166,11 @@
           <t>3:22.907</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2791,6 +2801,11 @@
           <t>3:26.266</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3226,6 +3241,11 @@
           <t>3:26.966</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3351,6 +3371,11 @@
           <t>3:27.826</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3851,6 +3876,11 @@
           <t>3:27.009</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4161,6 +4191,11 @@
           <t>1:46.398</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5953,6 +5988,11 @@
           <t>1:48.391</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7383,6 +7423,11 @@
           <t>3:44.159</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10215,6 +10260,11 @@
           <t>3:26.912</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10872,6 +10922,11 @@
           <t>3:36.139</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11137,6 +11192,11 @@
           <t>45844</t>
         </is>
       </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>45846</t>
@@ -11342,6 +11402,11 @@
           <t>42049</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="T173" t="inlineStr">
         <is>
           <t>52286</t>
@@ -11417,6 +11482,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="T174" t="inlineStr">
         <is>
           <t>36151</t>
@@ -12214,9 +12284,19 @@
           <t>1:31.393</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>36458</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>36459</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
@@ -14839,6 +14919,11 @@
           <t>3:28.258</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15156,6 +15241,11 @@
           <t>3:22.133</t>
         </is>
       </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15916,6 +16006,11 @@
           <t>3:28.558</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16231,6 +16326,11 @@
           <t>3:23.850</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16411,6 +16511,11 @@
           <t>3:30.426</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16591,6 +16696,11 @@
           <t>3:31.806</t>
         </is>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19720,6 +19830,11 @@
           <t>3:30.833</t>
         </is>
       </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -19780,6 +19895,11 @@
           <t>3:31.005</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -20175,6 +20295,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="T312" t="inlineStr">
         <is>
           <t>36151</t>
@@ -20385,6 +20510,11 @@
           <t>42049</t>
         </is>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="T315" t="inlineStr">
         <is>
           <t>52286</t>
@@ -21976,6 +22106,11 @@
           <t>3:25.596</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -22229,6 +22364,11 @@
           <t>3:36.942</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -23444,6 +23584,11 @@
           <t>3:35.548</t>
         </is>
       </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25602,6 +25747,11 @@
           <t>1:45.216</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -25922,6 +26072,11 @@
           <t>1:46.471</t>
         </is>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -26118,6 +26273,11 @@
           <t>3:18.369</t>
         </is>
       </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -26314,6 +26474,11 @@
           <t>3:20.132</t>
         </is>
       </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -27103,6 +27268,11 @@
           <t>3:47.157</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28373,6 +28543,11 @@
           <t>3:39.423</t>
         </is>
       </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -28433,6 +28608,11 @@
           <t>1:51.003</t>
         </is>
       </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -32392,6 +32572,11 @@
           <t>1:39.925</t>
         </is>
       </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -34916,6 +35101,11 @@
           <t>1:37.235</t>
         </is>
       </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -35291,6 +35481,11 @@
           <t>1:35.007</t>
         </is>
       </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -35791,6 +35986,11 @@
           <t>1:35.391</t>
         </is>
       </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -35916,6 +36116,11 @@
           <t>1:35.745</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -36856,6 +37061,11 @@
           <t>1:42.905</t>
         </is>
       </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -43738,6 +43948,11 @@
           <t>0:36.897</t>
         </is>
       </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -44043,6 +44258,11 @@
           <t>0:40.382</t>
         </is>
       </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -44163,6 +44383,11 @@
           <t>0:36.789</t>
         </is>
       </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -46808,6 +47033,11 @@
           <t>0:42.284</t>
         </is>
       </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -47790,6 +48020,11 @@
           <t>0:40.081</t>
         </is>
       </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -50130,6 +50365,11 @@
           <t>0:34.385</t>
         </is>
       </c>
+      <c r="S783" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -50955,6 +51195,11 @@
           <t>0:38.602</t>
         </is>
       </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
       <c r="S796" t="inlineStr">
         <is>
           <t>36458</t>
@@ -51920,6 +52165,11 @@
           <t>0:37.192</t>
         </is>
       </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -52370,6 +52620,11 @@
           <t>0:37.973</t>
         </is>
       </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -54250,6 +54505,11 @@
           <t>0:36.368</t>
         </is>
       </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -54855,6 +55115,11 @@
           <t>0:37.095</t>
         </is>
       </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -57410,6 +57675,11 @@
           <t>0:42.088</t>
         </is>
       </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -58640,6 +58910,11 @@
           <t>0:33.843</t>
         </is>
       </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -63153,6 +63428,11 @@
           <t>1:44.798</t>
         </is>
       </c>
+      <c r="R990" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -63277,6 +63557,11 @@
           <t>1:57.017</t>
         </is>
       </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -65465,6 +65750,11 @@
           <t>0:40.671</t>
         </is>
       </c>
+      <c r="R1026" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -66110,6 +66400,11 @@
           <t>0:36.451</t>
         </is>
       </c>
+      <c r="R1036" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -66956,6 +67251,11 @@
           <t>0:34.155</t>
         </is>
       </c>
+      <c r="S1049" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -68538,6 +68838,11 @@
           <t>1:36.723</t>
         </is>
       </c>
+      <c r="R1074" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -68868,6 +69173,11 @@
           <t>1:40.923</t>
         </is>
       </c>
+      <c r="R1079" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -69131,6 +69441,11 @@
           <t>1:45.120</t>
         </is>
       </c>
+      <c r="R1083" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -70111,6 +70426,11 @@
           <t>1:37.381</t>
         </is>
       </c>
+      <c r="S1098" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -71977,6 +72297,11 @@
           <t>0:39.578</t>
         </is>
       </c>
+      <c r="R1126" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -72694,6 +73019,11 @@
           <t>0:40.605</t>
         </is>
       </c>
+      <c r="R1137" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
@@ -73684,6 +74014,11 @@
           <t>0:36.608</t>
         </is>
       </c>
+      <c r="R1152" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
       <c r="S1152" t="inlineStr">
         <is>
           <t>36458</t>
@@ -74287,6 +74622,11 @@
           <t>0:35.513</t>
         </is>
       </c>
+      <c r="R1161" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -74347,6 +74687,11 @@
       <c r="P1162" t="inlineStr">
         <is>
           <t>0:36.024</t>
+        </is>
+      </c>
+      <c r="S1162" t="inlineStr">
+        <is>
+          <t>36155</t>
         </is>
       </c>
     </row>
@@ -80090,7 +80435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83569,6 +83914,314 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Viktor</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MELANTEV</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Dmitrii</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EKIMOV</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>36449</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Emanuel</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>PORTELA</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ahmadreza</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TALEBIAN</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BRIGDEN-JONES</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Gabor</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SZABO</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
+++ b/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
@@ -6053,6 +6053,11 @@
           <t>1:51.633</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8430,6 +8435,11 @@
           <t>3:08.236</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14409,6 +14419,11 @@
           <t>1:52.705</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18765,6 +18780,11 @@
           <t>3:09.942</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -23976,6 +23996,11 @@
           <t>3:11.352</t>
         </is>
       </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -44448,6 +44473,11 @@
           <t>0:36.961</t>
         </is>
       </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -45563,6 +45593,11 @@
           <t>0:42.738</t>
         </is>
       </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -55485,6 +55520,11 @@
           <t>0:36.816</t>
         </is>
       </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -58480,6 +58520,11 @@
           <t>0:43.037</t>
         </is>
       </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -66663,6 +66708,11 @@
           <t>0:36.809</t>
         </is>
       </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -67948,6 +67998,11 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>0:43.084</t>
+        </is>
+      </c>
+      <c r="R1060" t="inlineStr">
+        <is>
+          <t>51823</t>
         </is>
       </c>
     </row>
@@ -80435,7 +80490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84222,6 +84277,72 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CAUWENBERGH</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BICKNELL</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Jaimee</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LOVETT</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
+++ b/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
@@ -6053,11 +6053,6 @@
           <t>1:51.633</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8435,11 +8430,6 @@
           <t>3:08.236</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14419,11 +14409,6 @@
           <t>1:52.705</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18780,11 +18765,6 @@
           <t>3:09.942</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -23996,11 +23976,6 @@
           <t>3:11.352</t>
         </is>
       </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -44473,11 +44448,6 @@
           <t>0:36.961</t>
         </is>
       </c>
-      <c r="R688" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -45593,11 +45563,6 @@
           <t>0:42.738</t>
         </is>
       </c>
-      <c r="R706" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -55520,11 +55485,6 @@
           <t>0:36.816</t>
         </is>
       </c>
-      <c r="R864" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -58520,11 +58480,6 @@
           <t>0:43.037</t>
         </is>
       </c>
-      <c r="R912" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -66708,11 +66663,6 @@
           <t>0:36.809</t>
         </is>
       </c>
-      <c r="R1040" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -67998,11 +67948,6 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>0:43.084</t>
-        </is>
-      </c>
-      <c r="R1060" t="inlineStr">
-        <is>
-          <t>51823</t>
         </is>
       </c>
     </row>
@@ -80490,7 +80435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84277,72 +84222,6 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Olivier</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>CAUWENBERGH</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Scotty</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>BICKNELL</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Jaimee</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>LOVETT</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
+++ b/events/Vichy_2010_WC/Vichy_2010_WC_Results.xlsx
@@ -3501,6 +3501,11 @@
           <t>3:28.406</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5688,6 +5693,11 @@
           <t>1:52.723</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>69076</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8925,6 +8935,11 @@
           <t>3:07.486</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11749,6 +11764,11 @@
           <t>46829</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>46833</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13979,6 +13999,11 @@
           <t>1:55.685</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>69076</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15436,6 +15461,11 @@
           <t>3:25.888</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -19210,6 +19240,11 @@
           <t>3:08.511</t>
         </is>
       </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -23522,6 +23557,11 @@
           <t>3:28.292</t>
         </is>
       </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -27600,6 +27640,11 @@
           <t>3:05.097</t>
         </is>
       </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -31937,6 +31982,11 @@
           <t>1:42.327</t>
         </is>
       </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -38811,6 +38861,11 @@
           <t>1:28.891</t>
         </is>
       </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -43828,6 +43883,11 @@
           <t>0:36.783</t>
         </is>
       </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -49085,6 +49145,11 @@
           <t>36141</t>
         </is>
       </c>
+      <c r="S763" t="inlineStr">
+        <is>
+          <t>36142</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -53820,6 +53885,11 @@
           <t>0:36.551</t>
         </is>
       </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -59945,6 +60015,11 @@
           <t>36141</t>
         </is>
       </c>
+      <c r="S935" t="inlineStr">
+        <is>
+          <t>36142</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -66854,6 +66929,11 @@
           <t>0:46.253</t>
         </is>
       </c>
+      <c r="R1043" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -69962,6 +70042,11 @@
           <t>1:27.727</t>
         </is>
       </c>
+      <c r="S1091" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -73759,6 +73844,11 @@
       <c r="R1148" t="inlineStr">
         <is>
           <t>36141</t>
+        </is>
+      </c>
+      <c r="S1148" t="inlineStr">
+        <is>
+          <t>36142</t>
         </is>
       </c>
     </row>
@@ -80435,7 +80525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84222,6 +84312,94 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Jost</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ZAKRASSEK</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Reiniel</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>TORRES RIVEAUX</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>46833</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Emilio</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LLAMENDO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>36142</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Yuri</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>POSTRIGAY</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
